--- a/event_registration_forms/040_off_site_retreat_employee_rsvp_form--event_registration_forms.xlsx
+++ b/event_registration_forms/040_off_site_retreat_employee_rsvp_form--event_registration_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -734,8 +734,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="46" customWidth="1" min="2" max="2"/>
-    <col width="46" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -763,12 +763,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_true,_'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': True, 'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -780,12 +780,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_false,_'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': False, 'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -797,12 +797,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'onsite',_'label':_'onsite'}</t>
+          <t>onsite</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'Onsite', 'label': 'Onsite'}</t>
+          <t>Onsite</t>
         </is>
       </c>
     </row>
@@ -814,12 +814,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'offsite',_'label':_'offsite'}</t>
+          <t>offsite</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'Offsite', 'label': 'Offsite'}</t>
+          <t>Offsite</t>
         </is>
       </c>
     </row>
@@ -831,12 +831,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'both',_'label':_'both'}</t>
+          <t>both</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'Both', 'label': 'Both'}</t>
+          <t>Both</t>
         </is>
       </c>
     </row>
@@ -848,12 +848,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'breakfast',_'label':_'breakfast'}</t>
+          <t>breakfast</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'Breakfast', 'label': 'Breakfast'}</t>
+          <t>Breakfast</t>
         </is>
       </c>
     </row>
@@ -865,12 +865,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'dinner',_'label':_'dinner'}</t>
+          <t>dinner</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'Dinner', 'label': 'Dinner'}</t>
+          <t>Dinner</t>
         </is>
       </c>
     </row>
@@ -882,12 +882,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'lunch',_'label':_'lunch'}</t>
+          <t>lunch</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 'Lunch', 'label': 'Lunch'}</t>
+          <t>Lunch</t>
         </is>
       </c>
     </row>
@@ -899,12 +899,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_'snacks',_'label':_'snacks'}</t>
+          <t>snacks</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 'Snacks', 'label': 'Snacks'}</t>
+          <t>Snacks</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_'confirmed',_'label':_'confirmed'}</t>
+          <t>confirmed</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': 'Confirmed', 'label': 'Confirmed'}</t>
+          <t>Confirmed</t>
         </is>
       </c>
     </row>
@@ -933,12 +933,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_'tentative',_'label':_'tentative'}</t>
+          <t>tentative</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': 'Tentative', 'label': 'Tentative'}</t>
+          <t>Tentative</t>
         </is>
       </c>
     </row>
@@ -950,12 +950,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'value':_'no_show',_'label':_'no_show'}</t>
+          <t>no_show</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'value': 'No Show', 'label': 'No Show'}</t>
+          <t>No Show</t>
         </is>
       </c>
     </row>
